--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -14092,7 +14092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H250"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.75" customWidth="1" min="1" max="1"/>
@@ -20333,6 +20333,104 @@
         </is>
       </c>
       <c r="H250" s="45" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="441" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B251" s="42" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C251" s="36" t="inlineStr">
+        <is>
+          <t>使用者回報</t>
+        </is>
+      </c>
+      <c r="D251" s="45" t="inlineStr">
+        <is>
+          <t>未進食</t>
+        </is>
+      </c>
+      <c r="E251" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" s="45" t="inlineStr">
+        <is>
+          <t>使用者明確回報早上沒有吃東西。</t>
+        </is>
+      </c>
+      <c r="H251" s="45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="441" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B252" s="42" t="inlineStr">
+        <is>
+          <t>午餐</t>
+        </is>
+      </c>
+      <c r="C252" s="36" t="inlineStr">
+        <is>
+          <t>使用者回報＋麥當勞台灣現售品項確認＋透明估算</t>
+        </is>
+      </c>
+      <c r="D252" s="45" t="inlineStr">
+        <is>
+          <t>麥當勞 雙層麥香魚 1 個 + 大薯 1 份</t>
+        </is>
+      </c>
+      <c r="E252" s="45" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="F252" s="45" t="n">
+        <v>958</v>
+      </c>
+      <c r="G252" s="45" t="inlineStr">
+        <is>
+          <t>麥當勞台灣官網目前可確認雙層麥香魚與大薯為現售品項。雙層麥香魚完整營養數字官網動態頁未直接顯示，本筆沿用公開歷史同品項資料約 485 kcal、蛋白質 23.2g、碳水 43.3g；大薯採近期整理約 473 kcal、蛋白質 7.4g、碳水 63g。合計約 958 kcal、蛋白質 30.6g、碳水 106.3g；實際配方或份量若有更新會有誤差。</t>
+        </is>
+      </c>
+      <c r="H252" s="45" t="n">
+        <v>106.3</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="441" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B253" s="42" t="inlineStr">
+        <is>
+          <t>午餐</t>
+        </is>
+      </c>
+      <c r="C253" s="36" t="inlineStr">
+        <is>
+          <t>使用者回報</t>
+        </is>
+      </c>
+      <c r="D253" s="45" t="inlineStr">
+        <is>
+          <t>額外蛋白質 52g</t>
+        </is>
+      </c>
+      <c r="E253" s="45" t="n">
+        <v>52</v>
+      </c>
+      <c r="F253" s="45" t="inlineStr"/>
+      <c r="G253" s="45" t="inlineStr">
+        <is>
+          <t>使用者回報午餐另外攝取蛋白質 52g；未提供來源、品牌、熱量或碳水，因此僅記錄蛋白質，其餘不猜。</t>
+        </is>
+      </c>
+      <c r="H253" s="45" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -3346,7 +3346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4502,6 +4502,26 @@
       </c>
       <c r="I39" s="218" t="n"/>
       <c r="J39" s="215" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="450" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B40" s="451" t="n"/>
+      <c r="C40" s="222" t="n"/>
+      <c r="D40" s="218" t="n"/>
+      <c r="E40" s="44" t="n"/>
+      <c r="F40" s="44" t="n"/>
+      <c r="G40" s="218" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H40" s="218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="218" t="n"/>
+      <c r="J40" s="215" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -14092,7 +14112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.75" customWidth="1" min="1" max="1"/>
@@ -20431,6 +20451,34 @@
         </is>
       </c>
       <c r="H253" s="45" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="441" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B254" s="42" t="inlineStr">
+        <is>
+          <t>晚餐</t>
+        </is>
+      </c>
+      <c r="C254" s="36" t="inlineStr">
+        <is>
+          <t>使用者回報＋Pizza Hut 台灣官方現售品項確認</t>
+        </is>
+      </c>
+      <c r="D254" s="45" t="inlineStr">
+        <is>
+          <t>Pizza Hut 極炙厚牛干貝海陸披薩 2 片</t>
+        </is>
+      </c>
+      <c r="E254" s="45" t="inlineStr"/>
+      <c r="F254" s="45" t="inlineStr"/>
+      <c r="G254" s="45" t="inlineStr">
+        <is>
+          <t>Pizza Hut 台灣官方目前現售『極炙厚牛干貝海陸』，配料含炭火風燒牛肉、干貝、櫛瓜、番茄、洋蔥、莫札瑞拉起司、BBQ醬、炭火燒肉醬與明太子醬。使用者回報吃 2 片；未提供餅皮，官方頁面亦未提供可直接核對的完整營養標示，因此蛋白質、碳水與熱量留空，不自行猜測。</t>
+        </is>
+      </c>
+      <c r="H254" s="45" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -14112,7 +14112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H254"/>
+  <dimension ref="A1:H255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.75" customWidth="1" min="1" max="1"/>
@@ -20479,6 +20479,36 @@
         </is>
       </c>
       <c r="H254" s="45" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="441" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B255" s="42" t="inlineStr">
+        <is>
+          <t>晚餐</t>
+        </is>
+      </c>
+      <c r="C255" s="36" t="inlineStr">
+        <is>
+          <t>使用者回報</t>
+        </is>
+      </c>
+      <c r="D255" s="45" t="inlineStr">
+        <is>
+          <t>晚間額外蛋白質 52g</t>
+        </is>
+      </c>
+      <c r="E255" s="45" t="n">
+        <v>52</v>
+      </c>
+      <c r="F255" s="45" t="inlineStr"/>
+      <c r="G255" s="45" t="inlineStr">
+        <is>
+          <t>使用者於 2026-09-14 00:44 延續 2026-09-13 晚餐與當日蛋白質紀錄，回報晚上另外喝了蛋白質 52g；依上下文歸入 2026-09-13 晚餐追加。未提供品牌、來源、熱量或碳水，因此僅記錄蛋白質 52g，其餘不猜。</t>
+        </is>
+      </c>
+      <c r="H255" s="45" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -14112,7 +14112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H255"/>
+  <dimension ref="A1:H258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.75" customWidth="1" min="1" max="1"/>
@@ -20509,6 +20509,104 @@
         </is>
       </c>
       <c r="H255" s="45" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="441" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B256" s="42" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C256" s="36" t="inlineStr">
+        <is>
+          <t>使用者回報＋既有固定估算</t>
+        </is>
+      </c>
+      <c r="D256" s="45" t="inlineStr">
+        <is>
+          <t>地瓜 1 份 + 雞胸肉 1 份</t>
+        </is>
+      </c>
+      <c r="E256" s="45" t="n">
+        <v>32</v>
+      </c>
+      <c r="F256" s="45" t="n">
+        <v>285</v>
+      </c>
+      <c r="G256" s="45" t="inlineStr">
+        <is>
+          <t>沿用追蹤表既有相同組合設定：地瓜 1 份約蛋白質 2g、碳水 35g、125 kcal；雞胸肉 1 份約蛋白質 30g、160 kcal。</t>
+        </is>
+      </c>
+      <c r="H256" s="45" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="441" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B257" s="42" t="inlineStr">
+        <is>
+          <t>午餐</t>
+        </is>
+      </c>
+      <c r="C257" s="36" t="inlineStr">
+        <is>
+          <t>使用者回報＋沿用既有同品項透明估算</t>
+        </is>
+      </c>
+      <c r="D257" s="45" t="inlineStr">
+        <is>
+          <t>三商鮮五丼 麻婆魚排套餐</t>
+        </is>
+      </c>
+      <c r="E257" s="45" t="n">
+        <v>30</v>
+      </c>
+      <c r="F257" s="45" t="n">
+        <v>850</v>
+      </c>
+      <c r="G257" s="45" t="inlineStr">
+        <is>
+          <t>沿用追蹤表 2026-08-18 相同品項估算：約蛋白質 30g、碳水 105g、850 kcal。店家未提供完整營養標示，實際熱量仍會受飯量、炸魚排吸油與麻婆醬份量影響。</t>
+        </is>
+      </c>
+      <c r="H257" s="45" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="441" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B258" s="42" t="inlineStr">
+        <is>
+          <t>午餐</t>
+        </is>
+      </c>
+      <c r="C258" s="36" t="inlineStr">
+        <is>
+          <t>使用者回報</t>
+        </is>
+      </c>
+      <c r="D258" s="45" t="inlineStr">
+        <is>
+          <t>額外蛋白質 52g</t>
+        </is>
+      </c>
+      <c r="E258" s="45" t="n">
+        <v>52</v>
+      </c>
+      <c r="F258" s="45" t="inlineStr"/>
+      <c r="G258" s="45" t="inlineStr">
+        <is>
+          <t>使用者回報午餐另外攝取蛋白質 52g；未提供來源、品牌、熱量或碳水，因此僅記錄蛋白質，其餘不猜。</t>
+        </is>
+      </c>
+      <c r="H258" s="45" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'有氧紀錄'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'動作基準'!$A$1:$K$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'動作基準'!$A$1:$K$18</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -2481,7 +2481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2557,10 +2557,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>上斜胸推</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>DRAX 槓片式腿推機</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>40</v>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>10–15（特殊動作可依既有表現調整）</t>
@@ -2573,43 +2575,41 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I2" s="449" t="inlineStr">
         <is>
-          <t>25kg×15/DBR1；25kg×13/DBR1；25kg×9/DBR0；20kg×12/DBR1</t>
+          <t>40kg×15/DBR4</t>
         </is>
       </c>
       <c r="J2" s="449" t="inlineStr">
         <is>
-          <t>疼痛／不適：暫不自動推薦重量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="K2" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練備註出現疼痛／不適；保留歷史重量，但下次先確認無痛，不依重量基準直接加載。</t>
+          <t>最近一次訓練缺少完整的理想工作組，但 40 kg 的非力竭組最穩定；下次先延續此重量再依 DBR 調整。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>保加利亞分腿蹲</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>10</v>
-      </c>
+          <t>上斜胸推</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>10–15（特殊動作可依既有表現調整）</t>
@@ -2626,38 +2626,38 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="449" t="inlineStr">
         <is>
-          <t>左10kg×15/DBR2；左10kg×15/DBR2；左10kg×12/DBR2；左10kg×12/DBR2；左10kg×13/DBR2；右10kg×10/DBR2；左10kg×12/DBR1；右10kg×10/DBR1</t>
+          <t>25kg×15/DBR1；25kg×13/DBR1；25kg×9/DBR0；20kg×12/DBR1</t>
         </is>
       </c>
       <c r="J3" s="449" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>疼痛／不適：暫不自動推薦重量</t>
         </is>
       </c>
       <c r="K3" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 10 kg 有 8 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練備註出現疼痛／不適；保留歷史重量，但下次先確認無痛，不依重量基準直接加載。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>划船</t>
+          <t>保加利亞分腿蹲</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.5</v>
+        <v>10</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2671,21 +2671,21 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="449" t="inlineStr">
         <is>
-          <t>26.5kg×15/DBR4；26.5kg×15/DBR2；30kg×13/DBR2；30kg×13/DBR0；30kg×13/DBR0</t>
+          <t>左10kg×15/DBR2；左10kg×15/DBR2；左10kg×12/DBR2；左10kg×12/DBR2；左10kg×13/DBR2；右10kg×10/DBR2；左10kg×12/DBR1；右10kg×10/DBR1</t>
         </is>
       </c>
       <c r="J4" s="449" t="inlineStr">
@@ -2695,18 +2695,18 @@
       </c>
       <c r="K4" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 26.5 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 10 kg 有 8 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>反向飛鳥</t>
+          <t>划船</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>26.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2720,21 +2720,21 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="449" t="inlineStr">
         <is>
-          <t>15kg×15/DBR3；15kg×15/DBR1；15kg×13/DBR1；15kg×13/DBR1；15kg×11/DBR1</t>
+          <t>26.5kg×15/DBR4；26.5kg×15/DBR2；30kg×13/DBR2；30kg×13/DBR0；30kg×13/DBR0</t>
         </is>
       </c>
       <c r="J5" s="449" t="inlineStr">
@@ -2744,18 +2744,18 @@
       </c>
       <c r="K5" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 15 kg 有 5 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 26.5 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>啞鈴側平舉</t>
+          <t>反向飛鳥</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2769,21 +2769,21 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="449" t="inlineStr">
         <is>
-          <t>10kg×15/DBR1；10kg×13/DBR1；10kg×14/DBR1；10kg×15/DBR0</t>
+          <t>15kg×15/DBR3；15kg×15/DBR1；15kg×13/DBR1；15kg×13/DBR1；15kg×11/DBR1</t>
         </is>
       </c>
       <c r="J6" s="449" t="inlineStr">
@@ -2793,18 +2793,18 @@
       </c>
       <c r="K6" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 10 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 15 kg 有 5 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>滑輪下拉</t>
+          <t>啞鈴側平舉</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37.5</v>
+        <v>10</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2818,21 +2818,21 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>37.5</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="449" t="inlineStr">
         <is>
-          <t>37.5kg×13/DBR2；37.5kg×13/DBR2；37.5kg×11/DBR1；37.5kg×8/DBR0</t>
+          <t>10kg×15/DBR1；10kg×13/DBR1；10kg×14/DBR1；10kg×15/DBR0</t>
         </is>
       </c>
       <c r="J7" s="449" t="inlineStr">
@@ -2842,18 +2842,18 @@
       </c>
       <c r="K7" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 37.5 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 10 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>睾丸繩下拉</t>
+          <t>滑輪下拉</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.25</v>
+        <v>37.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2867,21 +2867,21 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6.25</v>
+        <v>37.5</v>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="449" t="inlineStr">
         <is>
-          <t>8.75kg×11/DBR0；8.75kg×10/DBR0；6.25kg×13/DBR0；6.25kg×13/DBR0；6.25kg×11/DBR0</t>
+          <t>37.5kg×13/DBR2；37.5kg×13/DBR2；37.5kg×11/DBR1；37.5kg×8/DBR0</t>
         </is>
       </c>
       <c r="J8" s="449" t="inlineStr">
@@ -2891,18 +2891,18 @@
       </c>
       <c r="K8" s="449" t="inlineStr">
         <is>
-          <t>最近一次已知組多為力竭；下次採該次較低重量重新建立 DBR1–3 的工作組。</t>
+          <t>最近一次訓練中 37.5 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>羅馬尼亞分腿蹲</t>
+          <t>睾丸繩下拉</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2916,21 +2916,21 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="G9" t="n">
         <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="449" t="inlineStr">
         <is>
-          <t>左10kg×15/DBR3；右10kg×15/DBR3；左10kg×15/DBR2；右10kg×15/DBR2；左10kg×15/DBR1；右10kg×11/DBR1；左10kg×11/DBR2；右10kg×11/DBR1</t>
+          <t>8.75kg×11/DBR0；8.75kg×10/DBR0；6.25kg×13/DBR0；6.25kg×13/DBR0；6.25kg×11/DBR0</t>
         </is>
       </c>
       <c r="J9" s="449" t="inlineStr">
@@ -2940,18 +2940,18 @@
       </c>
       <c r="K9" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 10 kg 有 8 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次已知組多為力竭；下次採該次較低重量重新建立 DBR1–3 的工作組。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>羅馬尼亞蹲</t>
+          <t>羅馬尼亞分腿蹲</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="449" t="inlineStr">
         <is>
-          <t>左自重×15/DBR3；右自重×15/DBR3；左5kg×15/DBR2；右5kg×8/DBR0；左5kg×14/DBR0；右5kg×14/DBR0；左5kg×14/DBR0；右5kg×14/DBR0</t>
+          <t>左10kg×15/DBR3；右10kg×15/DBR3；左10kg×15/DBR2；右10kg×15/DBR2；左10kg×15/DBR1；右10kg×11/DBR1；左10kg×11/DBR2；右10kg×11/DBR1</t>
         </is>
       </c>
       <c r="J10" s="449" t="inlineStr">
@@ -2989,18 +2989,18 @@
       </c>
       <c r="K10" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 5 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 10 kg 有 8 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>腿內收</t>
+          <t>羅馬尼亞蹲</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37.5</v>
+        <v>5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>37.5</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="449" t="inlineStr">
         <is>
-          <t>37.5kg×13/DBR2；37.5kg×13/DBR1；37.5kg×13/DBR1；37.5kg×13/DBR0</t>
+          <t>左自重×15/DBR3；右自重×15/DBR3；左5kg×15/DBR2；右5kg×8/DBR0；左5kg×14/DBR0；右5kg×14/DBR0；左5kg×14/DBR0；右5kg×14/DBR0</t>
         </is>
       </c>
       <c r="J11" s="449" t="inlineStr">
@@ -3038,18 +3038,18 @@
       </c>
       <c r="K11" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 37.5 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 5 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>腿外展</t>
+          <t>腿內收</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>37.5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3063,21 +3063,21 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>37.5</v>
       </c>
       <c r="G12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="449" t="inlineStr">
         <is>
-          <t>40.8kg×15/DBR4；48.75kg×15/DBR1；45kg×15/DBR1；45kg×12/DBR2；45kg×15/DBR2</t>
+          <t>37.5kg×13/DBR2；37.5kg×13/DBR1；37.5kg×13/DBR1；37.5kg×13/DBR0</t>
         </is>
       </c>
       <c r="J12" s="449" t="inlineStr">
@@ -3087,18 +3087,18 @@
       </c>
       <c r="K12" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 45 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 37.5 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>腿後勾</t>
+          <t>腿外展</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3116,17 +3116,17 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" s="449" t="inlineStr">
         <is>
-          <t>40kg×15/DBR3；47kg×15/DBR1；47kg×12/DBR1；47kg×13/DBR0</t>
+          <t>40.8kg×15/DBR4；48.75kg×15/DBR1；45kg×15/DBR1；45kg×12/DBR2；45kg×15/DBR2</t>
         </is>
       </c>
       <c r="J13" s="449" t="inlineStr">
@@ -3136,18 +3136,18 @@
       </c>
       <c r="K13" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 47 kg 有 2 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 45 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>腿推舉</t>
+          <t>腿後勾</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3161,21 +3161,21 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="449" t="inlineStr">
         <is>
-          <t>40kg×16/DBR3；40kg×18/DBR2；40kg×16/DBR1；40kg×16/DBR0</t>
+          <t>40kg×15/DBR3；47kg×15/DBR1；47kg×12/DBR1；47kg×13/DBR0</t>
         </is>
       </c>
       <c r="J14" s="449" t="inlineStr">
@@ -3185,17 +3185,19 @@
       </c>
       <c r="K14" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 40 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 47 kg 有 2 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>臀推機</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>腿推舉</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>40</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>10–15（特殊動作可依既有表現調整）</t>
@@ -3208,43 +3210,41 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" s="449" t="inlineStr">
         <is>
-          <t>20kg×12/DBR3；20kg×12/DBR2；20kg×12/DBR2</t>
+          <t>40kg×16/DBR3；40kg×18/DBR2；40kg×16/DBR1；40kg×16/DBR0</t>
         </is>
       </c>
       <c r="J15" s="449" t="inlineStr">
         <is>
-          <t>疼痛／不適：暫不自動推薦重量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="K15" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練備註出現疼痛／不適；保留歷史重量，但下次先確認無痛，不依重量基準直接加載。</t>
+          <t>最近一次訓練中 40 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>蝴蝶機夾胸</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>25</v>
-      </c>
+          <t>臀推機</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>10–15（特殊動作可依既有表現調整）</t>
@@ -3257,42 +3257,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" s="449" t="inlineStr">
         <is>
-          <t>25kg×15/DBR3；20kg×15/DBR0；25kg×7/DBR0；20kg×13/DBR0</t>
+          <t>20kg×12/DBR3；20kg×12/DBR2；20kg×12/DBR2</t>
         </is>
       </c>
       <c r="J16" s="449" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>疼痛／不適：暫不自動推薦重量</t>
         </is>
       </c>
       <c r="K16" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 25 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練備註出現疼痛／不適；保留歷史重量，但下次先確認無痛，不依重量基準直接加載。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>飛鳥夾胸</t>
+          <t>蝴蝶機夾胸</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3306,36 +3306,85 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="449" t="inlineStr">
         <is>
+          <t>25kg×15/DBR3；20kg×15/DBR0；25kg×7/DBR0；20kg×13/DBR0</t>
+        </is>
+      </c>
+      <c r="J17" s="449" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="K17" s="449" t="inlineStr">
+        <is>
+          <t>最近一次訓練中 25 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>飛鳥夾胸</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10–15（特殊動作可依既有表現調整）</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1–3；最後一組可視情況 DBR0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>20</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="449" t="inlineStr">
+        <is>
           <t>20kg×15/DBR3；20kg×14/DBR2；20kg×12/DBR1；20kg×10/DBR0</t>
         </is>
       </c>
-      <c r="J17" s="449" t="inlineStr">
+      <c r="J18" s="449" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="K17" s="449" t="inlineStr">
+      <c r="K18" s="449" t="inlineStr">
         <is>
           <t>最近一次訓練中 20 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K17"/>
+  <autoFilter ref="A1:K18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11755,18 +11804,40 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="403" t="n"/>
-      <c r="B204" s="34" t="n"/>
-      <c r="C204" s="34" t="n"/>
-      <c r="D204" s="410" t="n"/>
-      <c r="E204" s="411" t="n"/>
-      <c r="F204" s="411" t="n"/>
-      <c r="G204" s="411" t="n"/>
+      <c r="A204" s="403" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B204" s="34" t="inlineStr">
+        <is>
+          <t>重訓</t>
+        </is>
+      </c>
+      <c r="C204" s="34" t="inlineStr">
+        <is>
+          <t>DRAX 槓片式腿推機</t>
+        </is>
+      </c>
+      <c r="D204" s="410" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" s="411" t="n">
+        <v>40</v>
+      </c>
+      <c r="F204" s="411" t="n">
+        <v>15</v>
+      </c>
+      <c r="G204" s="411" t="n">
+        <v>4</v>
+      </c>
       <c r="H204" s="412">
         <f>IF(OR(E204="",F204=""),"",E204*F204)</f>
         <v/>
       </c>
-      <c r="I204" s="44" t="n"/>
+      <c r="I204" s="44" t="inlineStr">
+        <is>
+          <t>使用者回報 40 kg × 15，DBR4；照片確認為 DRAX 槓片式腿推機。重量按使用者回報記錄，不另加機台／滑軌自重；此動作與既有『腿推舉』分開建立基準。</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="403" t="n"/>

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -2585,11 +2585,11 @@
         <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2" s="449" t="inlineStr">
         <is>
-          <t>40kg×15/DBR4</t>
+          <t>40kg×15/DBR4；40kg×15/DBR3</t>
         </is>
       </c>
       <c r="J2" s="449" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="K2" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練缺少完整的理想工作組，但 40 kg 的非力竭組最穩定；下次先延續此重量再依 DBR 調整。</t>
+          <t>最近一次訓練中 40 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
@@ -11840,18 +11840,40 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="403" t="n"/>
-      <c r="B205" s="34" t="n"/>
-      <c r="C205" s="34" t="n"/>
-      <c r="D205" s="410" t="n"/>
-      <c r="E205" s="411" t="n"/>
-      <c r="F205" s="411" t="n"/>
-      <c r="G205" s="411" t="n"/>
+      <c r="A205" s="403" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B205" s="34" t="inlineStr">
+        <is>
+          <t>重訓</t>
+        </is>
+      </c>
+      <c r="C205" s="34" t="inlineStr">
+        <is>
+          <t>DRAX 槓片式腿推機</t>
+        </is>
+      </c>
+      <c r="D205" s="410" t="n">
+        <v>2</v>
+      </c>
+      <c r="E205" s="411" t="n">
+        <v>40</v>
+      </c>
+      <c r="F205" s="411" t="n">
+        <v>15</v>
+      </c>
+      <c r="G205" s="411" t="n">
+        <v>3</v>
+      </c>
       <c r="H205" s="412">
         <f>IF(OR(E205="",F205=""),"",E205*F205)</f>
         <v/>
       </c>
-      <c r="I205" s="44" t="n"/>
+      <c r="I205" s="44" t="inlineStr">
+        <is>
+          <t>重量未重複提供，沿用上一組 40 kg。</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="403" t="n"/>

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -2585,11 +2585,11 @@
         <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2" s="449" t="inlineStr">
         <is>
-          <t>40kg×15/DBR4；40kg×15/DBR3</t>
+          <t>40kg×15/DBR4；40kg×15/DBR3；40kg×15/DBR1</t>
         </is>
       </c>
       <c r="J2" s="449" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="K2" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 40 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 40 kg 有 2 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
@@ -11876,18 +11876,40 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="403" t="n"/>
-      <c r="B206" s="34" t="n"/>
-      <c r="C206" s="34" t="n"/>
-      <c r="D206" s="410" t="n"/>
-      <c r="E206" s="411" t="n"/>
-      <c r="F206" s="411" t="n"/>
-      <c r="G206" s="411" t="n"/>
+      <c r="A206" s="403" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B206" s="34" t="inlineStr">
+        <is>
+          <t>重訓</t>
+        </is>
+      </c>
+      <c r="C206" s="34" t="inlineStr">
+        <is>
+          <t>DRAX 槓片式腿推機</t>
+        </is>
+      </c>
+      <c r="D206" s="410" t="n">
+        <v>3</v>
+      </c>
+      <c r="E206" s="411" t="n">
+        <v>40</v>
+      </c>
+      <c r="F206" s="411" t="n">
+        <v>15</v>
+      </c>
+      <c r="G206" s="411" t="n">
+        <v>1</v>
+      </c>
       <c r="H206" s="412">
         <f>IF(OR(E206="",F206=""),"",E206*F206)</f>
         <v/>
       </c>
-      <c r="I206" s="44" t="n"/>
+      <c r="I206" s="44" t="inlineStr">
+        <is>
+          <t>重量未重複提供，沿用上一組 40 kg。照片中腳位為踏板中上區、約肩寬。</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="403" t="n"/>

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -2582,14 +2582,14 @@
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" s="449" t="inlineStr">
         <is>
-          <t>40kg×15/DBR4；40kg×15/DBR3；40kg×15/DBR1</t>
+          <t>40kg×15/DBR4；40kg×15/DBR3；40kg×15/DBR1；40kg×12/DBR2</t>
         </is>
       </c>
       <c r="J2" s="449" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="K2" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 40 kg 有 2 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 40 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
@@ -11912,18 +11912,40 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="403" t="n"/>
-      <c r="B207" s="34" t="n"/>
-      <c r="C207" s="34" t="n"/>
-      <c r="D207" s="410" t="n"/>
-      <c r="E207" s="411" t="n"/>
-      <c r="F207" s="411" t="n"/>
-      <c r="G207" s="411" t="n"/>
+      <c r="A207" s="403" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B207" s="34" t="inlineStr">
+        <is>
+          <t>重訓</t>
+        </is>
+      </c>
+      <c r="C207" s="34" t="inlineStr">
+        <is>
+          <t>DRAX 槓片式腿推機</t>
+        </is>
+      </c>
+      <c r="D207" s="410" t="n">
+        <v>4</v>
+      </c>
+      <c r="E207" s="411" t="n">
+        <v>40</v>
+      </c>
+      <c r="F207" s="411" t="n">
+        <v>12</v>
+      </c>
+      <c r="G207" s="411" t="n">
+        <v>2</v>
+      </c>
       <c r="H207" s="412">
         <f>IF(OR(E207="",F207=""),"",E207*F207)</f>
         <v/>
       </c>
-      <c r="I207" s="44" t="n"/>
+      <c r="I207" s="44" t="inlineStr">
+        <is>
+          <t>重量未重複提供，沿用上一組 40 kg。</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="403" t="n"/>

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -3161,21 +3161,21 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>47</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="449" t="inlineStr">
         <is>
-          <t>40kg×15/DBR3；47kg×15/DBR1；47kg×12/DBR1；47kg×13/DBR0</t>
+          <t>47kg×15/DBR2；47kg×12/DBR2</t>
         </is>
       </c>
       <c r="J14" s="449" t="inlineStr">
@@ -11948,32 +11948,76 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="403" t="n"/>
-      <c r="B208" s="34" t="n"/>
-      <c r="C208" s="34" t="n"/>
-      <c r="D208" s="410" t="n"/>
-      <c r="E208" s="411" t="n"/>
-      <c r="F208" s="411" t="n"/>
-      <c r="G208" s="411" t="n"/>
+      <c r="A208" s="403" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B208" s="34" t="inlineStr">
+        <is>
+          <t>重訓</t>
+        </is>
+      </c>
+      <c r="C208" s="34" t="inlineStr">
+        <is>
+          <t>腿後勾</t>
+        </is>
+      </c>
+      <c r="D208" s="410" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" s="411" t="n">
+        <v>47</v>
+      </c>
+      <c r="F208" s="411" t="n">
+        <v>15</v>
+      </c>
+      <c r="G208" s="411" t="n">
+        <v>2</v>
+      </c>
       <c r="H208" s="412">
         <f>IF(OR(E208="",F208=""),"",E208*F208)</f>
         <v/>
       </c>
-      <c r="I208" s="44" t="n"/>
+      <c r="I208" s="44" t="inlineStr">
+        <is>
+          <t>使用者回報 47 kg × 15，DBR2；照片為坐姿腿後勾機。</t>
+        </is>
+      </c>
     </row>
     <row r="209">
-      <c r="A209" s="403" t="n"/>
-      <c r="B209" s="34" t="n"/>
-      <c r="C209" s="34" t="n"/>
-      <c r="D209" s="410" t="n"/>
-      <c r="E209" s="411" t="n"/>
-      <c r="F209" s="411" t="n"/>
-      <c r="G209" s="411" t="n"/>
+      <c r="A209" s="403" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B209" s="34" t="inlineStr">
+        <is>
+          <t>重訓</t>
+        </is>
+      </c>
+      <c r="C209" s="34" t="inlineStr">
+        <is>
+          <t>腿後勾</t>
+        </is>
+      </c>
+      <c r="D209" s="410" t="n">
+        <v>2</v>
+      </c>
+      <c r="E209" s="411" t="n">
+        <v>47</v>
+      </c>
+      <c r="F209" s="411" t="n">
+        <v>12</v>
+      </c>
+      <c r="G209" s="411" t="n">
+        <v>2</v>
+      </c>
       <c r="H209" s="412">
         <f>IF(OR(E209="",F209=""),"",E209*F209)</f>
         <v/>
       </c>
-      <c r="I209" s="44" t="n"/>
+      <c r="I209" s="44" t="inlineStr">
+        <is>
+          <t>重量未重複提供，沿用上一組 47 kg。</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="403" t="n"/>

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -3171,11 +3171,11 @@
         <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="449" t="inlineStr">
         <is>
-          <t>47kg×15/DBR2；47kg×12/DBR2</t>
+          <t>47kg×15/DBR2；47kg×12/DBR2；47kg×12/DBR1</t>
         </is>
       </c>
       <c r="J14" s="449" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="K14" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 47 kg 有 2 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 47 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
@@ -12020,18 +12020,40 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="403" t="n"/>
-      <c r="B210" s="34" t="n"/>
-      <c r="C210" s="34" t="n"/>
-      <c r="D210" s="410" t="n"/>
-      <c r="E210" s="411" t="n"/>
-      <c r="F210" s="411" t="n"/>
-      <c r="G210" s="411" t="n"/>
+      <c r="A210" s="403" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B210" s="34" t="inlineStr">
+        <is>
+          <t>重訓</t>
+        </is>
+      </c>
+      <c r="C210" s="34" t="inlineStr">
+        <is>
+          <t>腿後勾</t>
+        </is>
+      </c>
+      <c r="D210" s="410" t="n">
+        <v>3</v>
+      </c>
+      <c r="E210" s="411" t="n">
+        <v>47</v>
+      </c>
+      <c r="F210" s="411" t="n">
+        <v>12</v>
+      </c>
+      <c r="G210" s="411" t="n">
+        <v>1</v>
+      </c>
       <c r="H210" s="412">
         <f>IF(OR(E210="",F210=""),"",E210*F210)</f>
         <v/>
       </c>
-      <c r="I210" s="44" t="n"/>
+      <c r="I210" s="44" t="inlineStr">
+        <is>
+          <t>重量未重複提供，沿用上一組 47 kg。</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="403" t="n"/>

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -3171,11 +3171,11 @@
         <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="449" t="inlineStr">
         <is>
-          <t>47kg×15/DBR2；47kg×12/DBR2；47kg×12/DBR1</t>
+          <t>47kg×15/DBR2；47kg×12/DBR2；47kg×12/DBR1；47kg×12/DBR0</t>
         </is>
       </c>
       <c r="J14" s="449" t="inlineStr">
@@ -12056,18 +12056,40 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="403" t="n"/>
-      <c r="B211" s="34" t="n"/>
-      <c r="C211" s="34" t="n"/>
-      <c r="D211" s="410" t="n"/>
-      <c r="E211" s="411" t="n"/>
-      <c r="F211" s="411" t="n"/>
-      <c r="G211" s="411" t="n"/>
+      <c r="A211" s="403" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B211" s="34" t="inlineStr">
+        <is>
+          <t>重訓</t>
+        </is>
+      </c>
+      <c r="C211" s="34" t="inlineStr">
+        <is>
+          <t>腿後勾</t>
+        </is>
+      </c>
+      <c r="D211" s="410" t="n">
+        <v>4</v>
+      </c>
+      <c r="E211" s="411" t="n">
+        <v>47</v>
+      </c>
+      <c r="F211" s="411" t="n">
+        <v>12</v>
+      </c>
+      <c r="G211" s="411" t="n">
+        <v>0</v>
+      </c>
       <c r="H211" s="412">
         <f>IF(OR(E211="",F211=""),"",E211*F211)</f>
         <v/>
       </c>
-      <c r="I211" s="44" t="n"/>
+      <c r="I211" s="44" t="inlineStr">
+        <is>
+          <t>重量未重複提供，沿用上一組 47 kg。</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="403" t="n"/>

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'有氧紀錄'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'動作基準'!$A$1:$K$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'動作基準'!$A$1:$K$19</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -2481,7 +2481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2606,10 +2606,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>上斜胸推</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>Gymleco Active Line 321 Chest Press</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25</v>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>10–15（特殊動作可依既有表現調整）</t>
@@ -2622,43 +2624,41 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="449" t="inlineStr">
         <is>
-          <t>25kg×15/DBR1；25kg×13/DBR1；25kg×9/DBR0；20kg×12/DBR1</t>
+          <t>25kg×15/DBR1；25kg×15/DBR1</t>
         </is>
       </c>
       <c r="J3" s="449" t="inlineStr">
         <is>
-          <t>疼痛／不適：暫不自動推薦重量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="K3" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練備註出現疼痛／不適；保留歷史重量，但下次先確認無痛，不依重量基準直接加載。</t>
+          <t>最近一次訓練中 25 kg 有 2 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>保加利亞分腿蹲</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>10</v>
-      </c>
+          <t>上斜胸推</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>10–15（特殊動作可依既有表現調整）</t>
@@ -2675,38 +2675,38 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="449" t="inlineStr">
         <is>
-          <t>左10kg×15/DBR2；左10kg×15/DBR2；左10kg×12/DBR2；左10kg×12/DBR2；左10kg×13/DBR2；右10kg×10/DBR2；左10kg×12/DBR1；右10kg×10/DBR1</t>
+          <t>25kg×15/DBR1；25kg×13/DBR1；25kg×9/DBR0；20kg×12/DBR1</t>
         </is>
       </c>
       <c r="J4" s="449" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>疼痛／不適：暫不自動推薦重量</t>
         </is>
       </c>
       <c r="K4" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 10 kg 有 8 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練備註出現疼痛／不適；保留歷史重量，但下次先確認無痛，不依重量基準直接加載。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>划船</t>
+          <t>保加利亞分腿蹲</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.5</v>
+        <v>10</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2720,21 +2720,21 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="449" t="inlineStr">
         <is>
-          <t>26.5kg×15/DBR4；26.5kg×15/DBR2；30kg×13/DBR2；30kg×13/DBR0；30kg×13/DBR0</t>
+          <t>左10kg×15/DBR2；左10kg×15/DBR2；左10kg×12/DBR2；左10kg×12/DBR2；左10kg×13/DBR2；右10kg×10/DBR2；左10kg×12/DBR1；右10kg×10/DBR1</t>
         </is>
       </c>
       <c r="J5" s="449" t="inlineStr">
@@ -2744,18 +2744,18 @@
       </c>
       <c r="K5" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 26.5 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 10 kg 有 8 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>反向飛鳥</t>
+          <t>划船</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>26.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2769,21 +2769,21 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="449" t="inlineStr">
         <is>
-          <t>15kg×15/DBR3；15kg×15/DBR1；15kg×13/DBR1；15kg×13/DBR1；15kg×11/DBR1</t>
+          <t>26.5kg×15/DBR4；26.5kg×15/DBR2；30kg×13/DBR2；30kg×13/DBR0；30kg×13/DBR0</t>
         </is>
       </c>
       <c r="J6" s="449" t="inlineStr">
@@ -2793,18 +2793,18 @@
       </c>
       <c r="K6" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 15 kg 有 5 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 26.5 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>啞鈴側平舉</t>
+          <t>反向飛鳥</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2818,21 +2818,21 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="449" t="inlineStr">
         <is>
-          <t>10kg×15/DBR1；10kg×13/DBR1；10kg×14/DBR1；10kg×15/DBR0</t>
+          <t>15kg×15/DBR3；15kg×15/DBR1；15kg×13/DBR1；15kg×13/DBR1；15kg×11/DBR1</t>
         </is>
       </c>
       <c r="J7" s="449" t="inlineStr">
@@ -2842,18 +2842,18 @@
       </c>
       <c r="K7" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 10 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 15 kg 有 5 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>滑輪下拉</t>
+          <t>啞鈴側平舉</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37.5</v>
+        <v>10</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2867,21 +2867,21 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>37.5</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="449" t="inlineStr">
         <is>
-          <t>37.5kg×13/DBR2；37.5kg×13/DBR2；37.5kg×11/DBR1；37.5kg×8/DBR0</t>
+          <t>10kg×15/DBR1；10kg×13/DBR1；10kg×14/DBR1；10kg×15/DBR0</t>
         </is>
       </c>
       <c r="J8" s="449" t="inlineStr">
@@ -2891,18 +2891,18 @@
       </c>
       <c r="K8" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 37.5 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 10 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>睾丸繩下拉</t>
+          <t>滑輪下拉</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.25</v>
+        <v>37.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2916,21 +2916,21 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.25</v>
+        <v>37.5</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="449" t="inlineStr">
         <is>
-          <t>8.75kg×11/DBR0；8.75kg×10/DBR0；6.25kg×13/DBR0；6.25kg×13/DBR0；6.25kg×11/DBR0</t>
+          <t>37.5kg×13/DBR2；37.5kg×13/DBR2；37.5kg×11/DBR1；37.5kg×8/DBR0</t>
         </is>
       </c>
       <c r="J9" s="449" t="inlineStr">
@@ -2940,18 +2940,18 @@
       </c>
       <c r="K9" s="449" t="inlineStr">
         <is>
-          <t>最近一次已知組多為力竭；下次採該次較低重量重新建立 DBR1–3 的工作組。</t>
+          <t>最近一次訓練中 37.5 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>羅馬尼亞分腿蹲</t>
+          <t>睾丸繩下拉</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="G10" t="n">
         <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="449" t="inlineStr">
         <is>
-          <t>左10kg×15/DBR3；右10kg×15/DBR3；左10kg×15/DBR2；右10kg×15/DBR2；左10kg×15/DBR1；右10kg×11/DBR1；左10kg×11/DBR2；右10kg×11/DBR1</t>
+          <t>8.75kg×11/DBR0；8.75kg×10/DBR0；6.25kg×13/DBR0；6.25kg×13/DBR0；6.25kg×11/DBR0</t>
         </is>
       </c>
       <c r="J10" s="449" t="inlineStr">
@@ -2989,18 +2989,18 @@
       </c>
       <c r="K10" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 10 kg 有 8 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次已知組多為力竭；下次採該次較低重量重新建立 DBR1–3 的工作組。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>羅馬尼亞蹲</t>
+          <t>羅馬尼亞分腿蹲</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="449" t="inlineStr">
         <is>
-          <t>左自重×15/DBR3；右自重×15/DBR3；左5kg×15/DBR2；右5kg×8/DBR0；左5kg×14/DBR0；右5kg×14/DBR0；左5kg×14/DBR0；右5kg×14/DBR0</t>
+          <t>左10kg×15/DBR3；右10kg×15/DBR3；左10kg×15/DBR2；右10kg×15/DBR2；左10kg×15/DBR1；右10kg×11/DBR1；左10kg×11/DBR2；右10kg×11/DBR1</t>
         </is>
       </c>
       <c r="J11" s="449" t="inlineStr">
@@ -3038,18 +3038,18 @@
       </c>
       <c r="K11" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 5 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 10 kg 有 8 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>腿內收</t>
+          <t>羅馬尼亞蹲</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37.5</v>
+        <v>5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3063,21 +3063,21 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>37.5</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="449" t="inlineStr">
         <is>
-          <t>37.5kg×13/DBR2；37.5kg×13/DBR1；37.5kg×13/DBR1；37.5kg×13/DBR0</t>
+          <t>左自重×15/DBR3；右自重×15/DBR3；左5kg×15/DBR2；右5kg×8/DBR0；左5kg×14/DBR0；右5kg×14/DBR0；左5kg×14/DBR0；右5kg×14/DBR0</t>
         </is>
       </c>
       <c r="J12" s="449" t="inlineStr">
@@ -3087,18 +3087,18 @@
       </c>
       <c r="K12" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 37.5 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 5 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>腿外展</t>
+          <t>腿內收</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>45</v>
+        <v>37.5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3112,21 +3112,21 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>37.5</v>
       </c>
       <c r="G13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" s="449" t="inlineStr">
         <is>
-          <t>40.8kg×15/DBR4；48.75kg×15/DBR1；45kg×15/DBR1；45kg×12/DBR2；45kg×15/DBR2</t>
+          <t>37.5kg×13/DBR2；37.5kg×13/DBR1；37.5kg×13/DBR1；37.5kg×13/DBR0</t>
         </is>
       </c>
       <c r="J13" s="449" t="inlineStr">
@@ -3136,18 +3136,18 @@
       </c>
       <c r="K13" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 45 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 37.5 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>腿後勾</t>
+          <t>腿外展</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3161,21 +3161,21 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="449" t="inlineStr">
         <is>
-          <t>47kg×15/DBR2；47kg×12/DBR2；47kg×12/DBR1；47kg×12/DBR0</t>
+          <t>40.8kg×15/DBR4；48.75kg×15/DBR1；45kg×15/DBR1；45kg×12/DBR2；45kg×15/DBR2</t>
         </is>
       </c>
       <c r="J14" s="449" t="inlineStr">
@@ -3185,18 +3185,18 @@
       </c>
       <c r="K14" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 47 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 45 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>腿推舉</t>
+          <t>腿後勾</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -3210,21 +3210,21 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="449" t="inlineStr">
         <is>
-          <t>40kg×16/DBR3；40kg×18/DBR2；40kg×16/DBR1；40kg×16/DBR0</t>
+          <t>47kg×15/DBR2；47kg×12/DBR2；47kg×12/DBR1；47kg×12/DBR0</t>
         </is>
       </c>
       <c r="J15" s="449" t="inlineStr">
@@ -3234,17 +3234,19 @@
       </c>
       <c r="K15" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 40 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練中 47 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>臀推機</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>腿推舉</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>40</v>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>10–15（特殊動作可依既有表現調整）</t>
@@ -3257,43 +3259,41 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" s="449" t="inlineStr">
         <is>
-          <t>20kg×12/DBR3；20kg×12/DBR2；20kg×12/DBR2</t>
+          <t>40kg×16/DBR3；40kg×18/DBR2；40kg×16/DBR1；40kg×16/DBR0</t>
         </is>
       </c>
       <c r="J16" s="449" t="inlineStr">
         <is>
-          <t>疼痛／不適：暫不自動推薦重量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="K16" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練備註出現疼痛／不適；保留歷史重量，但下次先確認無痛，不依重量基準直接加載。</t>
+          <t>最近一次訓練中 40 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>蝴蝶機夾胸</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>25</v>
-      </c>
+          <t>臀推機</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>10–15（特殊動作可依既有表現調整）</t>
@@ -3306,42 +3306,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" s="449" t="inlineStr">
         <is>
-          <t>25kg×15/DBR3；20kg×15/DBR0；25kg×7/DBR0；20kg×13/DBR0</t>
+          <t>20kg×12/DBR3；20kg×12/DBR2；20kg×12/DBR2</t>
         </is>
       </c>
       <c r="J17" s="449" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>疼痛／不適：暫不自動推薦重量</t>
         </is>
       </c>
       <c r="K17" s="449" t="inlineStr">
         <is>
-          <t>最近一次訓練中 25 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+          <t>最近一次訓練備註出現疼痛／不適；保留歷史重量，但下次先確認無痛，不依重量基準直接加載。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>飛鳥夾胸</t>
+          <t>蝴蝶機夾胸</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3355,36 +3355,85 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="449" t="inlineStr">
         <is>
+          <t>25kg×15/DBR3；20kg×15/DBR0；25kg×7/DBR0；20kg×13/DBR0</t>
+        </is>
+      </c>
+      <c r="J18" s="449" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="K18" s="449" t="inlineStr">
+        <is>
+          <t>最近一次訓練中 25 kg 有 1 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>飛鳥夾胸</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>20</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10–15（特殊動作可依既有表現調整）</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1–3；最後一組可視情況 DBR0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="449" t="inlineStr">
+        <is>
           <t>20kg×15/DBR3；20kg×14/DBR2；20kg×12/DBR1；20kg×10/DBR0</t>
         </is>
       </c>
-      <c r="J18" s="449" t="inlineStr">
+      <c r="J19" s="449" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="K18" s="449" t="inlineStr">
+      <c r="K19" s="449" t="inlineStr">
         <is>
           <t>最近一次訓練中 20 kg 有 3 組落在約 8–20 下、DBR1–3；以可重複的工作組表現優先，不直接選最高重量。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K18"/>
+  <autoFilter ref="A1:K19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12092,32 +12141,76 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="403" t="n"/>
-      <c r="B212" s="34" t="n"/>
-      <c r="C212" s="34" t="n"/>
-      <c r="D212" s="410" t="n"/>
-      <c r="E212" s="411" t="n"/>
-      <c r="F212" s="411" t="n"/>
-      <c r="G212" s="411" t="n"/>
+      <c r="A212" s="403" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B212" s="34" t="inlineStr">
+        <is>
+          <t>重訓</t>
+        </is>
+      </c>
+      <c r="C212" s="34" t="inlineStr">
+        <is>
+          <t>Gymleco Active Line 321 Chest Press</t>
+        </is>
+      </c>
+      <c r="D212" s="410" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" s="411" t="n">
+        <v>25</v>
+      </c>
+      <c r="F212" s="411" t="n">
+        <v>15</v>
+      </c>
+      <c r="G212" s="411" t="n">
+        <v>1</v>
+      </c>
       <c r="H212" s="412">
         <f>IF(OR(E212="",F212=""),"",E212*F212)</f>
         <v/>
       </c>
-      <c r="I212" s="44" t="n"/>
+      <c r="I212" s="44" t="inlineStr">
+        <is>
+          <t>使用者確認插銷位於 25 kg；照片確認機型為 Gymleco Active Line 321 Chest Press。</t>
+        </is>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="403" t="n"/>
-      <c r="B213" s="34" t="n"/>
-      <c r="C213" s="34" t="n"/>
-      <c r="D213" s="410" t="n"/>
-      <c r="E213" s="411" t="n"/>
-      <c r="F213" s="411" t="n"/>
-      <c r="G213" s="411" t="n"/>
+      <c r="A213" s="403" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B213" s="34" t="inlineStr">
+        <is>
+          <t>重訓</t>
+        </is>
+      </c>
+      <c r="C213" s="34" t="inlineStr">
+        <is>
+          <t>Gymleco Active Line 321 Chest Press</t>
+        </is>
+      </c>
+      <c r="D213" s="410" t="n">
+        <v>2</v>
+      </c>
+      <c r="E213" s="411" t="n">
+        <v>25</v>
+      </c>
+      <c r="F213" s="411" t="n">
+        <v>15</v>
+      </c>
+      <c r="G213" s="411" t="n">
+        <v>1</v>
+      </c>
       <c r="H213" s="412">
         <f>IF(OR(E213="",F213=""),"",E213*F213)</f>
         <v/>
       </c>
-      <c r="I213" s="44" t="n"/>
+      <c r="I213" s="44" t="inlineStr">
+        <is>
+          <t>重量未重複提供，沿用上一組 25 kg。</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="403" t="n"/>

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
         <v>15</v>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="I3" s="449" t="inlineStr">
         <is>
-          <t>25kg×15/DBR1；25kg×15/DBR1</t>
+          <t>25kg×15/DBR1；25kg×15/DBR1；30kg×15/DBR1</t>
         </is>
       </c>
       <c r="J3" s="449" t="inlineStr">
@@ -12213,18 +12213,36 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="403" t="n"/>
-      <c r="B214" s="34" t="n"/>
-      <c r="C214" s="34" t="n"/>
-      <c r="D214" s="410" t="n"/>
-      <c r="E214" s="411" t="n"/>
-      <c r="F214" s="411" t="n"/>
-      <c r="G214" s="411" t="n"/>
+      <c r="A214" s="403" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B214" s="34" t="inlineStr">
+        <is>
+          <t>重訓</t>
+        </is>
+      </c>
+      <c r="C214" s="34" t="inlineStr">
+        <is>
+          <t>Gymleco Active Line 321 Chest Press</t>
+        </is>
+      </c>
+      <c r="D214" s="410" t="n">
+        <v>3</v>
+      </c>
+      <c r="E214" s="411" t="n">
+        <v>30</v>
+      </c>
+      <c r="F214" s="411" t="n">
+        <v>15</v>
+      </c>
+      <c r="G214" s="411" t="n">
+        <v>1</v>
+      </c>
       <c r="H214" s="412">
         <f>IF(OR(E214="",F214=""),"",E214*F214)</f>
         <v/>
       </c>
-      <c r="I214" s="44" t="n"/>
+      <c r="I214" s="44" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="403" t="n"/>

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -14448,7 +14448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H258"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.75" customWidth="1" min="1" max="1"/>
@@ -20943,6 +20943,34 @@
         </is>
       </c>
       <c r="H258" s="45" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="441" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B259" s="42" t="inlineStr">
+        <is>
+          <t>晚餐</t>
+        </is>
+      </c>
+      <c r="C259" s="36" t="inlineStr">
+        <is>
+          <t>使用者回報</t>
+        </is>
+      </c>
+      <c r="D259" s="45" t="inlineStr">
+        <is>
+          <t>鹽水雞：雞胸肉 1 塊 + 6 樣菜</t>
+        </is>
+      </c>
+      <c r="E259" s="45" t="inlineStr"/>
+      <c r="F259" s="45" t="inlineStr"/>
+      <c r="G259" s="45" t="inlineStr">
+        <is>
+          <t>使用者回報晚餐吃鹽水雞：雞胸肉 1 塊與 6 樣菜。未提供雞胸肉重量、6 樣菜的種類與份量，因此依規則不猜蛋白質、碳水或熱量，營養數值暫留空白。</t>
+        </is>
+      </c>
+      <c r="H259" s="45" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -3444,7 +3444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4620,6 +4620,22 @@
       </c>
       <c r="I40" s="218" t="n"/>
       <c r="J40" s="215" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="450" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B41" s="451" t="n"/>
+      <c r="C41" s="222" t="n"/>
+      <c r="D41" s="218" t="n"/>
+      <c r="E41" s="44" t="n"/>
+      <c r="F41" s="44" t="n"/>
+      <c r="G41" s="218" t="n"/>
+      <c r="H41" s="218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="218" t="n"/>
+      <c r="J41" s="215" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -14464,7 +14464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.75" customWidth="1" min="1" max="1"/>
@@ -20987,6 +20987,104 @@
         </is>
       </c>
       <c r="H259" s="45" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="441" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B260" s="42" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C260" s="36" t="inlineStr">
+        <is>
+          <t>使用者回報＋既有固定估算</t>
+        </is>
+      </c>
+      <c r="D260" s="45" t="inlineStr">
+        <is>
+          <t>地瓜 1 份 + 雞胸肉 1 份</t>
+        </is>
+      </c>
+      <c r="E260" s="45" t="n">
+        <v>32</v>
+      </c>
+      <c r="F260" s="45" t="n">
+        <v>285</v>
+      </c>
+      <c r="G260" s="45" t="inlineStr">
+        <is>
+          <t>沿用追蹤表既有相同組合設定：地瓜 1 份約蛋白質 2g、碳水 35g、125 kcal；雞胸肉 1 份約蛋白質 30g、160 kcal。</t>
+        </is>
+      </c>
+      <c r="H260" s="45" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="441" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B261" s="42" t="inlineStr">
+        <is>
+          <t>午餐</t>
+        </is>
+      </c>
+      <c r="C261" s="36" t="inlineStr">
+        <is>
+          <t>使用者回報</t>
+        </is>
+      </c>
+      <c r="D261" s="45" t="inlineStr">
+        <is>
+          <t>額外蛋白質 52g</t>
+        </is>
+      </c>
+      <c r="E261" s="45" t="n">
+        <v>52</v>
+      </c>
+      <c r="F261" s="45" t="inlineStr"/>
+      <c r="G261" s="45" t="inlineStr">
+        <is>
+          <t>使用者回報中午攝取蛋白質 52g；未提供來源、品牌、熱量或碳水，因此僅記錄蛋白質，其餘不猜。</t>
+        </is>
+      </c>
+      <c r="H261" s="45" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="441" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B262" s="42" t="inlineStr">
+        <is>
+          <t>晚餐</t>
+        </is>
+      </c>
+      <c r="C262" s="36" t="inlineStr">
+        <is>
+          <t>使用者回報＋照片份量透明估算</t>
+        </is>
+      </c>
+      <c r="D262" s="45" t="inlineStr">
+        <is>
+          <t>雞肉飯 1 碗 + 滷蛋 1 顆 + 豆製品配料</t>
+        </is>
+      </c>
+      <c r="E262" s="45" t="n">
+        <v>45</v>
+      </c>
+      <c r="F262" s="45" t="n">
+        <v>800</v>
+      </c>
+      <c r="G262" s="45" t="inlineStr">
+        <is>
+          <t>依使用者照片可見：白飯、較多撕雞肉、滷蛋 1 顆，以及豆干／豆皮類豆製品配料。實際重量未量測，先透明估算整碗約蛋白質 45g、碳水 90g、800 kcal；主要誤差來自白飯份量、雞肉實際重量、豆製品種類與醬汁用量，熱量可能上下浮動約 150–200 kcal。</t>
+        </is>
+      </c>
+      <c r="H262" s="45" t="n">
+        <v>90</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/30天重建追蹤.xlsx
+++ b/30天重建追蹤.xlsx
@@ -3444,7 +3444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4636,6 +4636,26 @@
       </c>
       <c r="I41" s="218" t="n"/>
       <c r="J41" s="215" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="450" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B42" s="451" t="n"/>
+      <c r="C42" s="222" t="n"/>
+      <c r="D42" s="218" t="n"/>
+      <c r="E42" s="44" t="n"/>
+      <c r="F42" s="44" t="n"/>
+      <c r="G42" s="218" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H42" s="218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="218" t="n"/>
+      <c r="J42" s="215" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
